--- a/data/industry/CFM/DDR.xlsx
+++ b/data/industry/CFM/DDR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D620F9E7-98A6-468F-A825-A71DCFB72B61}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71C70F1-732B-481D-9FCC-6A7012563D9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="673" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -457,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -1101,7 +1101,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E28" s="12">
         <v>40</v>
@@ -1121,7 +1121,7 @@
         <v>46056</v>
       </c>
       <c r="C29" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>8</v>
@@ -1133,6 +1133,98 @@
         <v>80</v>
       </c>
       <c r="G29" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>40</v>
+      </c>
+      <c r="F30" s="12">
+        <v>80</v>
+      </c>
+      <c r="G30" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>40</v>
+      </c>
+      <c r="F31" s="12">
+        <v>80</v>
+      </c>
+      <c r="G31" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>40</v>
+      </c>
+      <c r="F32" s="12">
+        <v>80</v>
+      </c>
+      <c r="G32" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>40</v>
+      </c>
+      <c r="F33" s="12">
+        <v>80</v>
+      </c>
+      <c r="G33" s="12">
         <v>50</v>
       </c>
     </row>
@@ -1145,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ECE58E1-E673-4989-AE5A-B8686BAF4454}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -1789,7 +1881,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E28" s="12">
         <v>11</v>
@@ -1809,7 +1901,7 @@
         <v>46056</v>
       </c>
       <c r="C29" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>8</v>
@@ -1822,6 +1914,98 @@
       </c>
       <c r="G29" s="12">
         <v>12.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>11.5</v>
+      </c>
+      <c r="F30" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="G30" s="12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>11.5</v>
+      </c>
+      <c r="F31" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="G31" s="12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>11.5</v>
+      </c>
+      <c r="F32" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="G32" s="12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F33" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G33" s="12">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1832,7 +2016,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E892F627-73C7-4D50-84EF-2BEC5382C9F2}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -2496,7 +2680,7 @@
         <v>46056</v>
       </c>
       <c r="C29" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>8</v>
@@ -2508,6 +2692,98 @@
         <v>25</v>
       </c>
       <c r="G29" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>11</v>
+      </c>
+      <c r="F30" s="12">
+        <v>25</v>
+      </c>
+      <c r="G30" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>11</v>
+      </c>
+      <c r="F31" s="12">
+        <v>25</v>
+      </c>
+      <c r="G31" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>11</v>
+      </c>
+      <c r="F32" s="12">
+        <v>25</v>
+      </c>
+      <c r="G32" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>11</v>
+      </c>
+      <c r="F33" s="12">
+        <v>25</v>
+      </c>
+      <c r="G33" s="12">
         <v>15</v>
       </c>
     </row>
@@ -2519,7 +2795,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98E7142-8EB2-4D50-8855-47B862F141C9}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -3198,6 +3474,98 @@
         <v>6.5</v>
       </c>
     </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>6.3</v>
+      </c>
+      <c r="F30" s="12">
+        <v>7.3</v>
+      </c>
+      <c r="G30" s="12">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>6.3</v>
+      </c>
+      <c r="F31" s="12">
+        <v>7.3</v>
+      </c>
+      <c r="G31" s="12">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>6.3</v>
+      </c>
+      <c r="F32" s="12">
+        <v>7.3</v>
+      </c>
+      <c r="G32" s="12">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F33" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G33" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3206,7 +3574,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3674D84-1184-43AD-82E1-AE4900944B12}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -3885,6 +4253,98 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F30" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G30" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F31" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G31" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F32" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G32" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F33" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G33" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3893,7 +4353,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADBDF414-6821-49E6-A1DF-C17838025248}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -4572,6 +5032,98 @@
         <v>36</v>
       </c>
     </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>32</v>
+      </c>
+      <c r="F30" s="12">
+        <v>40</v>
+      </c>
+      <c r="G30" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>32</v>
+      </c>
+      <c r="F31" s="12">
+        <v>40</v>
+      </c>
+      <c r="G31" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>32</v>
+      </c>
+      <c r="F32" s="12">
+        <v>40</v>
+      </c>
+      <c r="G32" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>32</v>
+      </c>
+      <c r="F33" s="12">
+        <v>40</v>
+      </c>
+      <c r="G33" s="12">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4580,7 +5132,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E0312D-9566-49D8-B0D1-D78DB0764F8E}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -5259,6 +5811,98 @@
         <v>30</v>
       </c>
     </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>28</v>
+      </c>
+      <c r="F30" s="12">
+        <v>32</v>
+      </c>
+      <c r="G30" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>28</v>
+      </c>
+      <c r="F31" s="12">
+        <v>32</v>
+      </c>
+      <c r="G31" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>28</v>
+      </c>
+      <c r="F32" s="12">
+        <v>32</v>
+      </c>
+      <c r="G32" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>28</v>
+      </c>
+      <c r="F33" s="12">
+        <v>32</v>
+      </c>
+      <c r="G33" s="12">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5267,7 +5911,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6397CE70-E09B-4668-A71C-5388D3A6C3B5}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -5946,6 +6590,98 @@
         <v>22</v>
       </c>
     </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="9">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="16">
+        <v>22</v>
+      </c>
+      <c r="F30" s="16">
+        <v>25</v>
+      </c>
+      <c r="G30" s="16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="16">
+        <v>22</v>
+      </c>
+      <c r="F31" s="16">
+        <v>25</v>
+      </c>
+      <c r="G31" s="16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="9">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="16">
+        <v>22</v>
+      </c>
+      <c r="F32" s="16">
+        <v>25</v>
+      </c>
+      <c r="G32" s="16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="16">
+        <v>24</v>
+      </c>
+      <c r="F33" s="16">
+        <v>27</v>
+      </c>
+      <c r="G33" s="16">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/industry/CFM/DDR.xlsx
+++ b/data/industry/CFM/DDR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71C70F1-732B-481D-9FCC-6A7012563D9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C97CD4-D744-40E3-985E-2CFEAE80341C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="673" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="673" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 16Gb 3200" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="DDR5 24Gb Major" sheetId="6" r:id="rId6"/>
     <sheet name="DDR5 16Gb Major" sheetId="7" r:id="rId7"/>
     <sheet name="DDR5 16Gb eTT" sheetId="8" r:id="rId8"/>
+    <sheet name="fig" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -192,6 +193,2707 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>DDR4 16Gb 3200</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'DDR4 16Gb eTT'!$B$2:$B$1133</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>45860</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45867</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45874</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45881</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45888</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45895</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45909</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45916</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45923</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45944</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45951</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45958</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45965</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45972</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45979</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46007</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46014</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46021</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46028</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46035</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46042</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DDR4 16Gb 3200'!$G$2:$G$1133</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>DDR4 16Gb eTT</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'DDR4 16Gb eTT'!$B$2:$B$1133</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>45860</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45867</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45874</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45881</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45888</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45895</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45909</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45916</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45923</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45944</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45951</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45958</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45965</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45972</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45979</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46007</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46014</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46021</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46028</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46035</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46042</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DDR4 16Gb eTT'!$G$2:$G$1133</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>DDR4 8Gb 3200</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'DDR4 16Gb eTT'!$B$2:$B$1133</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>45860</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45867</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45874</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45881</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45888</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45895</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45909</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45916</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45923</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45944</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45951</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45958</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45965</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45972</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45979</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46007</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46014</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46021</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46028</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46035</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46042</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DDR4 8Gb 3200'!$G$2:$G$1133</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>DDR4 8Gb eTT</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'DDR4 16Gb eTT'!$B$2:$B$1133</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>45860</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45867</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45874</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45881</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45888</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45895</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45909</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45916</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45923</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45944</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45951</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45958</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45965</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45972</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45979</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46007</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46014</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46021</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46028</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46035</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46042</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DDR4 8Gb eTT'!$G$2:$G$1133</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7.4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>DDR4 4Gb eTT</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'DDR4 16Gb eTT'!$B$2:$B$1133</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>45860</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45867</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45874</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45881</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45888</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45895</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45909</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45916</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45923</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45944</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45951</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45958</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45965</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45972</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45979</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46007</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46014</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46021</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46028</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46035</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46042</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DDR4 4Gb eTT'!$G$2:$G$1133</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.35</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.52</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.68</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.72</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.72</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.85</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.85</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>DDR5 24Gb Major</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'DDR4 16Gb eTT'!$B$2:$B$1133</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>45860</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45867</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45874</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45881</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45888</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45895</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45909</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45916</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45923</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45944</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45951</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45958</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45965</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45972</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45979</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46007</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46014</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46021</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46028</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46035</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46042</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DDR5 24Gb Major'!$G$2:$G$1133</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.95</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.95</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>36</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>DDR5 16Gb Major</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'DDR4 16Gb eTT'!$B$2:$B$1133</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>45860</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45867</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45874</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45881</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45888</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45895</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45909</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45916</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45923</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45944</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45951</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45958</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45965</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45972</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45979</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46007</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46014</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46021</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46028</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46035</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46042</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DDR5 16Gb Major'!$G$2:$G$1133</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.95</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.05</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>DDR5 16Gb eTT</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'DDR4 16Gb eTT'!$B$2:$B$1133</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>45860</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45867</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45874</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45881</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45888</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45895</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45909</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45916</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45923</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45944</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45951</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45958</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45965</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45972</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45979</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45993</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46007</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46014</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46021</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46028</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46035</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46042</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'DDR5 16Gb eTT'!$G$2:$G$1133</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="1132"/>
+                <c:pt idx="0">
+                  <c:v>4.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="860404639"/>
+        <c:axId val="324361167"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="860404639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46203"/>
+          <c:min val="45870"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy/mm;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="324361167"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="324361167"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_);[Red]\(#,##0\)" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="860404639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>209549</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>676274</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F95ADF4C-15A8-496E-AA4F-D2152BC3B8C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6686,4 +9388,16 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125E0383-8D21-4789-B003-A94DDDB82616}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/data/industry/CFM/DDR.xlsx
+++ b/data/industry/CFM/DDR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C97CD4-D744-40E3-985E-2CFEAE80341C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59EAA5DD-C3BC-4CA4-A2CD-A7FC79C776F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="673" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="673" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 16Gb 3200" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -335,6 +335,12 @@
                 <c:pt idx="31">
                   <c:v>46091</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -440,10 +446,16 @@
                 <c:pt idx="31">
                   <c:v>50</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>50</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
@@ -570,6 +582,12 @@
                 <c:pt idx="31">
                   <c:v>46091</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -675,10 +693,16 @@
                 <c:pt idx="31">
                   <c:v>15</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>15</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
@@ -805,6 +829,12 @@
                 <c:pt idx="31">
                   <c:v>46091</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -910,10 +940,16 @@
                 <c:pt idx="31">
                   <c:v>15</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>15</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
@@ -1040,6 +1076,12 @@
                 <c:pt idx="31">
                   <c:v>46091</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1145,10 +1187,16 @@
                 <c:pt idx="31">
                   <c:v>7.4</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7.4</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
@@ -1275,6 +1323,12 @@
                 <c:pt idx="31">
                   <c:v>46091</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1380,10 +1434,16 @@
                 <c:pt idx="31">
                   <c:v>2.7</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2.7</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
@@ -1510,6 +1570,12 @@
                 <c:pt idx="31">
                   <c:v>46091</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1615,10 +1681,16 @@
                 <c:pt idx="31">
                   <c:v>36</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>36</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
@@ -1747,6 +1819,12 @@
                 <c:pt idx="31">
                   <c:v>46091</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1852,10 +1930,16 @@
                 <c:pt idx="31">
                   <c:v>30</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>30</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
@@ -1984,6 +2068,12 @@
                 <c:pt idx="31">
                   <c:v>46091</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2089,10 +2179,16 @@
                 <c:pt idx="31">
                   <c:v>26</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>26</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000007-2AD4-4C0C-AB30-E4B2588E5D2E}"/>
@@ -3159,7 +3255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -3930,6 +4026,52 @@
         <v>50</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>40</v>
+      </c>
+      <c r="F34" s="12">
+        <v>80</v>
+      </c>
+      <c r="G34" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>40</v>
+      </c>
+      <c r="F35" s="12">
+        <v>80</v>
+      </c>
+      <c r="G35" s="12">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3939,7 +4081,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ECE58E1-E673-4989-AE5A-B8686BAF4454}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -4710,6 +4852,52 @@
         <v>15</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F34" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G34" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F35" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G35" s="12">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4718,7 +4906,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E892F627-73C7-4D50-84EF-2BEC5382C9F2}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -5489,6 +5677,52 @@
         <v>15</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>11</v>
+      </c>
+      <c r="F34" s="12">
+        <v>25</v>
+      </c>
+      <c r="G34" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>11</v>
+      </c>
+      <c r="F35" s="12">
+        <v>25</v>
+      </c>
+      <c r="G35" s="12">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5497,7 +5731,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98E7142-8EB2-4D50-8855-47B862F141C9}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -6268,6 +6502,52 @@
         <v>7.4</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F34" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G34" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F35" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G35" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6276,7 +6556,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3674D84-1184-43AD-82E1-AE4900944B12}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -7047,6 +7327,52 @@
         <v>2.7</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F34" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G34" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F35" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G35" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7055,7 +7381,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADBDF414-6821-49E6-A1DF-C17838025248}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -7826,6 +8152,52 @@
         <v>36</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>32</v>
+      </c>
+      <c r="F34" s="12">
+        <v>40</v>
+      </c>
+      <c r="G34" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>32</v>
+      </c>
+      <c r="F35" s="12">
+        <v>40</v>
+      </c>
+      <c r="G35" s="12">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7834,7 +8206,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E0312D-9566-49D8-B0D1-D78DB0764F8E}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -8605,6 +8977,52 @@
         <v>30</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>28</v>
+      </c>
+      <c r="F34" s="12">
+        <v>32</v>
+      </c>
+      <c r="G34" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>28</v>
+      </c>
+      <c r="F35" s="12">
+        <v>32</v>
+      </c>
+      <c r="G35" s="12">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8613,7 +9031,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6397CE70-E09B-4668-A71C-5388D3A6C3B5}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -9381,6 +9799,52 @@
         <v>27</v>
       </c>
       <c r="G33" s="16">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="9">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="16">
+        <v>24</v>
+      </c>
+      <c r="F34" s="16">
+        <v>27</v>
+      </c>
+      <c r="G34" s="16">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="16">
+        <v>24</v>
+      </c>
+      <c r="F35" s="16">
+        <v>27</v>
+      </c>
+      <c r="G35" s="16">
         <v>26</v>
       </c>
     </row>
